--- a/data/describe/few_shot/cluster/few_shot_cluster_label.xlsx
+++ b/data/describe/few_shot/cluster/few_shot_cluster_label.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amaca253\Documents\datomatisation\datomatisation-dev\data\describe\few_shot\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amaca253\Documents\datomatisation\datomatisation-dev\data\describe\few_shot\cluster\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78889294-78BB-4255-BCAD-621BFE71C098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ED98494-88AE-4708-A970-0279C6048A32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{75A2F0CC-120C-46DD-B882-D3F79246B1DD}"/>
+    <workbookView xWindow="29940" yWindow="1140" windowWidth="22425" windowHeight="15225" xr2:uid="{75A2F0CC-120C-46DD-B882-D3F79246B1DD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -60,9 +60,6 @@
     <t>Here is the cluster description representing a typical person in that cluster: ```This cluster reflects individuals who are steady, grounded, and emotionally attuned, often providing a sense of reliability and calm in their interactions. Their main strengths are very high groundedness and relatively high empathy, which allow them to remain composed in challenging situations while understanding and supporting others effectively. On other traits such as modesty, conscientiousness, considerateness, casualness, and slightly lower reservedness, they generally show average tendencies, balancing approachability with thoughtful consideration. Overall, this cluster describes dependable, empathetic individuals who combine strong stability and emotional insight with moderate social and practical traits.```</t>
   </si>
   <si>
-    <t>devoted friend</t>
-  </si>
-  <si>
     <t>Here is the cluster description representing a typical dog in that cluster: ```This cluster describes dogs that are highly loving and adaptable companions for their human families, with average energy levels, but tend to be less amiable and neat, particularly in their interactions with other dogs.
 Their primary strengths include a strong affection for their family, a kind disposition towards young children, and a good level of adaptability to various environments, while maintaining a normal capacity for play and learning.
 They exhibit weaknesses in their interactions with other dogs, as they are described as slightly low on "friendly and neat," indicating they may not play well with other canines and are also likely to be less tidy, possibly prone to drooling or shedding.´´´</t>
@@ -78,13 +75,16 @@
   </si>
   <si>
     <t>Here is the cluster description representing a typical person in that cluster: ```This cluster represents individuals who are lively, confident, and socially engaging, often bringing energy and enthusiasm to their interactions. Their main strength lies in being highly outgoing, which allows them to connect easily with others and energize social situations. On other traits such as groundedness, modesty, conscientiousness, considerateness, conceptual thinking, meticulousness, and self-reliance, they generally fall within the average range, displaying balanced and steady behavior without extreme tendencies. Overall, this cluster describes sociable, energetic individuals who combine high friendliness and expressiveness with reliably moderate traits across other areas.´´´</t>
+  </si>
+  <si>
+    <t>Devoted friend</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -96,12 +96,6 @@
       <sz val="11"/>
       <name val="Times New Roman"/>
       <family val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -124,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -135,7 +129,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -453,7 +446,7 @@
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="54.26953125" customWidth="1"/>
+    <col min="1" max="1" width="82.81640625" customWidth="1"/>
     <col min="2" max="2" width="43" customWidth="1"/>
   </cols>
   <sheetData>
@@ -467,7 +460,7 @@
     </row>
     <row r="2" spans="1:2" ht="176" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>4</v>
@@ -475,9 +468,9 @@
     </row>
     <row r="3" spans="1:2" ht="168" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
     </row>
@@ -485,24 +478,24 @@
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="246.5" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="210" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" ht="154" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="4" t="s">
         <v>7</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
